--- a/data/initial_tracker.xlsx
+++ b/data/initial_tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hclo365-my.sharepoint.com/personal/giridharkr_hcltech_com/Documents/01-ASM COE/23-MAS Industrialization/Mondelez/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giridharkr\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{108FB7C4-B154-49D2-A148-4FAFC4434EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AEDADD-A8B2-4377-849A-21F7082CDA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="11" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="Detailed Task Tracker" sheetId="4" r:id="rId5"/>
     <sheet name="Lists" sheetId="10" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="table1">Lists!#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,8 +40,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="584">
   <si>
     <t>Recommendations aligned</t>
   </si>
@@ -1144,9 +1169,6 @@
     <t>Karol, Tanveer, data owners</t>
   </si>
   <si>
-    <t>Soumya, Pooja</t>
-  </si>
-  <si>
     <t>Deliverable Control Log</t>
   </si>
   <si>
@@ -1267,9 +1289,6 @@
     <t>AMS Application Support Inventory</t>
   </si>
   <si>
-    <t>Soumya</t>
-  </si>
-  <si>
     <t>Inventory exceptions captured</t>
   </si>
   <si>
@@ -1789,7 +1808,13 @@
     <t xml:space="preserve">Be realistic → product model is still early-stage and evolving </t>
   </si>
   <si>
-    <t>-</t>
+    <t>Workstream2</t>
+  </si>
+  <si>
+    <t>Deliverable ID</t>
+  </si>
+  <si>
+    <t>ID2</t>
   </si>
 </sst>
 </file>
@@ -1799,7 +1824,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1818,11 +1843,6 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Carlito"/>
     </font>
     <font>
@@ -1878,6 +1898,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="HCLTech Roobert"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="HCLTech Roobert"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -2022,7 +2057,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2030,124 +2065,127 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2156,11 +2194,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="73">
     <dxf>
       <font>
         <b/>
@@ -2229,6 +2270,61 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2537,6 +2633,42 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2561,6 +2693,41 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2646,27 +2813,10 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="HCLTech Roobert"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2680,27 +2830,6 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="HCLTech Roobert"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -2737,9 +2866,82 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Carlito"/>
+        <sz val="11"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
     </dxf>
@@ -2752,7 +2954,130 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <name val="Carlito"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="HCLTech Roobert"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
     </dxf>
@@ -3428,112 +3753,84 @@
 </styleSheet>
 </file>
 
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
-<file path=xl/namedSheetViews/namedSheetView2.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
-<file path=xl/namedSheetViews/namedSheetView3.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
-<file path=xl/namedSheetViews/namedSheetView4.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeamRoleMatrix" displayName="TeamRoleMatrix" ref="A1:H10" headerRowDxfId="55" dataDxfId="53" totalsRowDxfId="51" headerRowBorderDxfId="54" tableBorderDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeamRoleMatrix" displayName="TeamRoleMatrix" ref="A1:H10" headerRowDxfId="72" dataDxfId="70" totalsRowDxfId="68" headerRowBorderDxfId="71" tableBorderDxfId="69">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="HCLTech Team Member" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Project Role" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Primary Accountability" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Key Outputs Owned" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Internal Cadence" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Backup / Support" dataDxfId="45"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Critical Watchouts" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="First 2-Week Focus" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="HCLTech Team Member" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Project Role" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Primary Accountability" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Key Outputs Owned" dataDxfId="64"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Internal Cadence" dataDxfId="63"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Backup / Support" dataDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Critical Watchouts" dataDxfId="61"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="First 2-Week Focus" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="WorkstreamOwnership" displayName="WorkstreamOwnership" ref="A1:J9" headerRowDxfId="42" dataDxfId="40" totalsRowDxfId="38" headerRowBorderDxfId="41" tableBorderDxfId="39">
-  <autoFilter ref="A1:J9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="WorkstreamOwnership" displayName="WorkstreamOwnership" ref="A1:J9" headerRowDxfId="59" dataDxfId="57" totalsRowDxfId="55" headerRowBorderDxfId="58" tableBorderDxfId="56">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="WS" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Workstream" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Phase" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Primary HCL Owner" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Supporting Team" dataDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Core Internal Responsibilities" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Committed Deliverables" dataDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Quality Reviewer" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Internal Due / Gate (TBC)" dataDxfId="29"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Notes" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="WS" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Workstream" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Phase" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Primary HCL Owner" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Supporting Team" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Core Internal Responsibilities" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Committed Deliverables" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Quality Reviewer" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Internal Due / Gate (TBC)" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Notes" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="DeliverableControl" displayName="DeliverableControl" ref="A4:L46">
-  <autoFilter ref="A4:L46" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="Giridhar"/>
-        <filter val="Giridhar, Pratik"/>
-        <filter val="Narasimha,Giridhar"/>
-        <filter val="Pooja, Giridhar"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Phase"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Workstream"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Deliverable"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Primary Owner"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Support"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Draft Due (TBC)" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Final Due (TBC)" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Status"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="QA Owner"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="Review Audience"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="Acceptance / Completion Evidence"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="DeliverableControl" displayName="DeliverableControl" ref="A4:M46" headerRowDxfId="44" dataDxfId="43" totalsRowDxfId="42">
+  <autoFilter ref="A4:M46" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Phase" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Workstream" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Deliverable" dataDxfId="38"/>
+    <tableColumn id="13" xr3:uid="{FF2B191C-C7D0-494A-94C6-901047368005}" name="ID2" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Primary Owner" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Support" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Draft Due (TBC)" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Final Due (TBC)" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Status" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="QA Owner" dataDxfId="32"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="Review Audience" dataDxfId="31"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="Acceptance / Completion Evidence" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="DetailedTaskTracker" displayName="DetailedTaskTracker" ref="A1:O40" headerRowDxfId="25" dataDxfId="23" totalsRowDxfId="21" headerRowBorderDxfId="24" tableBorderDxfId="22">
-  <autoFilter ref="A1:O40" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Giridhar Krishnagiri"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Task ID" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Phase" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Workstream" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Activity / Task" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Primary Owner" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Support" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Start Date" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Due Date" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Internal Checkpoint" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Status" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="RAG" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Priority" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Dependency / Input Needed" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="Next Action" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="Due Health" dataDxfId="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="DetailedTaskTracker" displayName="DetailedTaskTracker" ref="A1:R40" headerRowDxfId="29" dataDxfId="28" totalsRowDxfId="27" headerRowBorderDxfId="25" tableBorderDxfId="26">
+  <autoFilter ref="A1:R40" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}"/>
+  <tableColumns count="18">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Task ID" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Phase" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Workstream" dataDxfId="22"/>
+    <tableColumn id="18" xr3:uid="{B35EDB4C-1E11-4730-8683-C707ACA73664}" name="Workstream2" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Activity / Task" dataDxfId="20"/>
+    <tableColumn id="16" xr3:uid="{8127AC71-1BDF-4ED0-B788-2111DF1E3377}" name="Deliverable" dataDxfId="19"/>
+    <tableColumn id="19" xr3:uid="{6F628818-4A01-4992-9E6B-AE1D200D4A85}" name="Deliverable ID" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Primary Owner" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Support" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Start Date" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Due Date" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Internal Checkpoint" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Status" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="RAG" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Priority" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Dependency / Input Needed" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="Next Action" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="Due Health" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3692,108 +3989,108 @@
   <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
     <row r="2" spans="2:2" ht="14.4">
-      <c r="B2" s="41" t="s">
-        <v>562</v>
+      <c r="B2" s="39" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="7" spans="2:2">
-      <c r="B7" s="42" t="s">
-        <v>565</v>
+      <c r="B7" s="40" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="14.4">
-      <c r="B22" s="41" t="s">
-        <v>577</v>
+      <c r="B22" s="39" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -3809,272 +4106,272 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="15.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5" style="10" customWidth="1"/>
-    <col min="3" max="3" width="40.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.59765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.09765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.69921875" style="10"/>
+    <col min="1" max="1" width="15.796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5" style="8" customWidth="1"/>
+    <col min="3" max="3" width="40.796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.09765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.69921875" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="25.2">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="37.799999999999997">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="37.799999999999997">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:8" ht="37.799999999999997">
+      <c r="A5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="50.4">
+      <c r="A6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="E6" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>542</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:8" ht="37.799999999999997">
-      <c r="A5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>553</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="50.4">
-      <c r="A6" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>543</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>544</v>
-      </c>
     </row>
     <row r="7" spans="1:8" ht="25.2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="50.4">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>554</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="12" t="s">
-        <v>551</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>552</v>
+      <c r="G8" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="25.2">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>559</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>558</v>
-      </c>
-      <c r="D9" s="12" t="s">
+      <c r="B9" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="11" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="37.799999999999997">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="14" t="s">
         <v>59</v>
       </c>
     </row>
@@ -4097,304 +4394,304 @@
   <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="8.5" style="8" customWidth="1"/>
-    <col min="2" max="2" width="30.796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.19921875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="23.09765625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="24.09765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.09765625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="54.796875" style="8" customWidth="1"/>
-    <col min="8" max="8" width="11.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.69921875" style="8"/>
+    <col min="1" max="1" width="8.5" style="6" customWidth="1"/>
+    <col min="2" max="2" width="30.796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="23.09765625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="24.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.09765625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="54.796875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="11.19921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.19921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.69921875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="9" customFormat="1" ht="36">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="36">
+      <c r="A1" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="29" t="s">
-        <v>560</v>
-      </c>
-      <c r="J1" s="30" t="s">
+      <c r="I1" s="27" t="s">
+        <v>558</v>
+      </c>
+      <c r="J1" s="28" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="36">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="I2" s="34">
+      <c r="I2" s="32">
         <v>46185</v>
       </c>
-      <c r="J2" s="35" t="s">
+      <c r="J2" s="33" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="54">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="31" t="s">
+        <v>553</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="32">
+        <v>46227</v>
+      </c>
+      <c r="J3" s="33" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="72">
+      <c r="A4" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>554</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>537</v>
+      </c>
+      <c r="I4" s="32">
+        <v>46227</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="54">
+      <c r="A5" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="31" t="s">
         <v>555</v>
       </c>
-      <c r="F3" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="H3" s="33" t="s">
+      <c r="F5" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="I3" s="34">
-        <v>46227</v>
-      </c>
-      <c r="J3" s="35" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="72">
-      <c r="A4" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="33" t="s">
+      <c r="I5" s="32">
+        <v>46262</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="54">
+      <c r="A6" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="I6" s="32">
+        <v>46262</v>
+      </c>
+      <c r="J6" s="33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="36">
+      <c r="A7" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="33" t="s">
-        <v>556</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>539</v>
-      </c>
-      <c r="I4" s="34">
-        <v>46227</v>
-      </c>
-      <c r="J4" s="35" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="54">
-      <c r="A5" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>557</v>
-      </c>
-      <c r="F5" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="H5" s="33" t="s">
+      <c r="E7" s="31" t="s">
+        <v>245</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="H7" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="I5" s="34">
-        <v>46262</v>
-      </c>
-      <c r="J5" s="35" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="54">
-      <c r="A6" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="G6" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="H6" s="33" t="s">
+      <c r="I7" s="32">
+        <v>46269</v>
+      </c>
+      <c r="J7" s="33" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="54">
+      <c r="A8" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>536</v>
+      </c>
+      <c r="I8" s="32">
+        <v>46283</v>
+      </c>
+      <c r="J8" s="33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="54">
+      <c r="A9" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="H9" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="I6" s="34">
-        <v>46262</v>
-      </c>
-      <c r="J6" s="35" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="36">
-      <c r="A7" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>245</v>
-      </c>
-      <c r="F7" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="G7" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="H7" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="I7" s="34">
-        <v>46269</v>
-      </c>
-      <c r="J7" s="35" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="54">
-      <c r="A8" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="F8" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="G8" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="H8" s="33" t="s">
-        <v>538</v>
-      </c>
-      <c r="I8" s="34">
-        <v>46283</v>
-      </c>
-      <c r="J8" s="35" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="54">
-      <c r="A9" s="36" t="s">
-        <v>583</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="F9" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="H9" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="I9" s="39">
+      <c r="I9" s="37">
         <v>46276</v>
       </c>
-      <c r="J9" s="40" t="s">
+      <c r="J9" s="38" t="s">
         <v>115</v>
       </c>
     </row>
@@ -4414,1690 +4711,1819 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="6.8984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="22.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.8984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="40.3984375" customWidth="1"/>
+    <col min="5" max="5" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="22.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.8984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="40.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.600000000000001" customHeight="1">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:13" ht="18.600000000000001" customHeight="1">
+      <c r="A1" s="45" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+    </row>
+    <row r="2" spans="1:13" ht="14.7" customHeight="1">
+      <c r="A2" s="47" t="s">
+        <v>559</v>
+      </c>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+    </row>
+    <row r="4" spans="1:13" ht="36">
+      <c r="A4" s="42" t="s">
         <v>369</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-    </row>
-    <row r="2" spans="1:12" ht="14.7" customHeight="1">
-      <c r="A2" s="46" t="s">
-        <v>561</v>
-      </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-    </row>
-    <row r="4" spans="1:12" ht="27.6">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="42" t="s">
         <v>370</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="42" t="s">
+        <v>583</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="G4" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>546</v>
+      </c>
+      <c r="I4" s="42" t="s">
+        <v>547</v>
+      </c>
+      <c r="J4" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="K4" s="42" t="s">
         <v>371</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="L4" s="42" t="s">
+        <v>372</v>
+      </c>
+      <c r="M4" s="42" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="31.2">
+      <c r="A5" s="43" t="s">
+        <v>374</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>375</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>374</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="H5" s="44">
+        <v>46182</v>
+      </c>
+      <c r="I5" s="44">
+        <v>46185</v>
+      </c>
+      <c r="J5" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="K5" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5" s="43" t="s">
+        <v>376</v>
+      </c>
+      <c r="M5" s="43" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="31.2">
+      <c r="A6" s="43" t="s">
+        <v>378</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>379</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>378</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" s="44">
+        <v>46182</v>
+      </c>
+      <c r="I6" s="44">
+        <v>46185</v>
+      </c>
+      <c r="J6" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="K6" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L6" s="43" t="s">
+        <v>380</v>
+      </c>
+      <c r="M6" s="43" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="31.2">
+      <c r="A7" s="43" t="s">
+        <v>382</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>383</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>382</v>
+      </c>
+      <c r="F7" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="H7" s="44">
+        <v>46179</v>
+      </c>
+      <c r="I7" s="44">
+        <v>46185</v>
+      </c>
+      <c r="J7" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="K7" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" s="43" t="s">
+        <v>367</v>
+      </c>
+      <c r="M7" s="43" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="31.2">
+      <c r="A8" s="43" t="s">
+        <v>385</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>386</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>385</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="H8" s="44">
+        <v>46179</v>
+      </c>
+      <c r="I8" s="44">
+        <v>46185</v>
+      </c>
+      <c r="J8" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="43" t="s">
+        <v>380</v>
+      </c>
+      <c r="M8" s="43" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="31.2">
+      <c r="A9" s="43" t="s">
+        <v>388</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>389</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>388</v>
+      </c>
+      <c r="F9" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="H9" s="44">
+        <v>46183</v>
+      </c>
+      <c r="I9" s="44">
+        <v>46185</v>
+      </c>
+      <c r="J9" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K9" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L9" s="43" t="s">
+        <v>380</v>
+      </c>
+      <c r="M9" s="43" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15.6">
+      <c r="A10" s="43" t="s">
+        <v>391</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>392</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>391</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="43" t="s">
+        <v>393</v>
+      </c>
+      <c r="H10" s="44">
+        <v>46209</v>
+      </c>
+      <c r="I10" s="44">
+        <v>46215</v>
+      </c>
+      <c r="J10" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K10" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L10" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M10" s="43" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15.6">
+      <c r="A11" s="43" t="s">
+        <v>396</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>397</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>396</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="H11" s="44">
+        <v>46209</v>
+      </c>
+      <c r="I11" s="44">
+        <v>46215</v>
+      </c>
+      <c r="J11" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L11" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M11" s="43" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15.6">
+      <c r="A12" s="43" t="s">
+        <v>399</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>400</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>399</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="43" t="s">
+        <v>401</v>
+      </c>
+      <c r="H12" s="44">
+        <v>46209</v>
+      </c>
+      <c r="I12" s="44">
+        <v>46215</v>
+      </c>
+      <c r="J12" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K12" s="43" t="s">
+        <v>401</v>
+      </c>
+      <c r="L12" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="M12" s="43" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.6">
+      <c r="A13" s="43" t="s">
+        <v>403</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>404</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>403</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>401</v>
+      </c>
+      <c r="H13" s="44">
+        <v>46209</v>
+      </c>
+      <c r="I13" s="44">
+        <v>46215</v>
+      </c>
+      <c r="J13" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L13" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M13" s="43" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15.6">
+      <c r="A14" s="43" t="s">
+        <v>406</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>407</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>406</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="43" t="s">
+        <v>411</v>
+      </c>
+      <c r="H14" s="44">
+        <v>46191</v>
+      </c>
+      <c r="I14" s="44">
+        <v>46198</v>
+      </c>
+      <c r="J14" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K14" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L14" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="M14" s="43" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.6">
+      <c r="A15" s="43" t="s">
+        <v>409</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>409</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="43" t="s">
+        <v>411</v>
+      </c>
+      <c r="H15" s="44">
+        <v>46191</v>
+      </c>
+      <c r="I15" s="44">
+        <v>46198</v>
+      </c>
+      <c r="J15" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K15" s="43" t="s">
+        <v>412</v>
+      </c>
+      <c r="L15" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="M15" s="43" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="31.2">
+      <c r="A16" s="43" t="s">
+        <v>414</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>415</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>414</v>
+      </c>
+      <c r="F16" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="H16" s="44">
+        <v>46191</v>
+      </c>
+      <c r="I16" s="44">
+        <v>46198</v>
+      </c>
+      <c r="J16" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K16" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L16" s="43" t="s">
+        <v>416</v>
+      </c>
+      <c r="M16" s="43" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15.6">
+      <c r="A17" s="43" t="s">
+        <v>418</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>419</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>418</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="H17" s="44">
+        <v>46191</v>
+      </c>
+      <c r="I17" s="44">
+        <v>46198</v>
+      </c>
+      <c r="J17" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K17" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L17" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="M17" s="43" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.6">
+      <c r="A18" s="43" t="s">
+        <v>421</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>422</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>421</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="43" t="s">
+        <v>423</v>
+      </c>
+      <c r="H18" s="44">
+        <v>46191</v>
+      </c>
+      <c r="I18" s="44">
+        <v>46198</v>
+      </c>
+      <c r="J18" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K18" s="43" t="s">
+        <v>423</v>
+      </c>
+      <c r="L18" s="43" t="s">
+        <v>424</v>
+      </c>
+      <c r="M18" s="43" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15.6">
+      <c r="A19" s="43" t="s">
+        <v>426</v>
+      </c>
+      <c r="B19" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>427</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>426</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="H19" s="44">
+        <v>46191</v>
+      </c>
+      <c r="I19" s="44">
+        <v>46198</v>
+      </c>
+      <c r="J19" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K19" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L19" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="M19" s="43" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="15.6">
+      <c r="A20" s="43" t="s">
+        <v>430</v>
+      </c>
+      <c r="B20" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="43" t="s">
+        <v>431</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>430</v>
+      </c>
+      <c r="F20" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="H20" s="44">
+        <v>46191</v>
+      </c>
+      <c r="I20" s="44">
+        <v>46198</v>
+      </c>
+      <c r="J20" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K20" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L20" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="M20" s="43" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15.6">
+      <c r="A21" s="43" t="s">
+        <v>433</v>
+      </c>
+      <c r="B21" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="43" t="s">
         <v>548</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" hidden="1">
-      <c r="A5" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="E21" s="43" t="s">
+        <v>433</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="43" t="s">
+        <v>401</v>
+      </c>
+      <c r="H21" s="44">
+        <v>46191</v>
+      </c>
+      <c r="I21" s="44">
+        <v>46198</v>
+      </c>
+      <c r="J21" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K21" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="L21" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="M21" s="43" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="31.2">
+      <c r="A22" s="43" t="s">
+        <v>435</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="43" t="s">
+        <v>436</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>435</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="H22" s="44">
+        <v>46248</v>
+      </c>
+      <c r="I22" s="44">
+        <v>46262</v>
+      </c>
+      <c r="J22" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K22" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L22" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M22" s="43" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="31.2">
+      <c r="A23" s="43" t="s">
+        <v>438</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" s="43" t="s">
+        <v>439</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>438</v>
+      </c>
+      <c r="F23" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" s="44">
+        <v>46251</v>
+      </c>
+      <c r="I23" s="44">
+        <v>46262</v>
+      </c>
+      <c r="J23" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K23" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L23" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M23" s="43" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="31.2">
+      <c r="A24" s="43" t="s">
+        <v>441</v>
+      </c>
+      <c r="B24" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="43" t="s">
+        <v>442</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>441</v>
+      </c>
+      <c r="F24" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="43" t="s">
+        <v>401</v>
+      </c>
+      <c r="H24" s="44">
+        <v>46248</v>
+      </c>
+      <c r="I24" s="44">
+        <v>46262</v>
+      </c>
+      <c r="J24" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K24" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L24" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M24" s="43" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="31.2">
+      <c r="A25" s="43" t="s">
+        <v>444</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>444</v>
+      </c>
+      <c r="F25" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="43" t="s">
+        <v>545</v>
+      </c>
+      <c r="H25" s="44">
+        <v>46255</v>
+      </c>
+      <c r="I25" s="44">
+        <v>46262</v>
+      </c>
+      <c r="J25" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K25" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L25" s="43" t="s">
+        <v>446</v>
+      </c>
+      <c r="M25" s="43" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="31.2">
+      <c r="A26" s="43" t="s">
+        <v>447</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>448</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>447</v>
+      </c>
+      <c r="F26" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="H26" s="44">
+        <v>46251</v>
+      </c>
+      <c r="I26" s="44">
+        <v>46262</v>
+      </c>
+      <c r="J26" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K26" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L26" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M26" s="43" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="31.2">
+      <c r="A27" s="43" t="s">
+        <v>450</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="43" t="s">
+        <v>451</v>
+      </c>
+      <c r="E27" s="43" t="s">
+        <v>450</v>
+      </c>
+      <c r="F27" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="H27" s="44">
+        <v>46251</v>
+      </c>
+      <c r="I27" s="44">
+        <v>46262</v>
+      </c>
+      <c r="J27" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K27" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L27" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M27" s="43" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="31.2">
+      <c r="A28" s="43" t="s">
+        <v>453</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>454</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>453</v>
+      </c>
+      <c r="F28" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="H28" s="44">
+        <v>46255</v>
+      </c>
+      <c r="I28" s="44">
+        <v>46262</v>
+      </c>
+      <c r="J28" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K28" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L28" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="M28" s="43" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="31.2">
+      <c r="A29" s="43" t="s">
+        <v>456</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" s="43" t="s">
+        <v>457</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>456</v>
+      </c>
+      <c r="F29" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="H29" s="44">
+        <v>46255</v>
+      </c>
+      <c r="I29" s="44">
+        <v>46262</v>
+      </c>
+      <c r="J29" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K29" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L29" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M29" s="43" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="31.2">
+      <c r="A30" s="43" t="s">
+        <v>459</v>
+      </c>
+      <c r="B30" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>460</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>459</v>
+      </c>
+      <c r="F30" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="H30" s="44">
+        <v>46255</v>
+      </c>
+      <c r="I30" s="44">
+        <v>46262</v>
+      </c>
+      <c r="J30" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K30" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L30" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M30" s="43" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="31.2">
+      <c r="A31" s="43" t="s">
+        <v>462</v>
+      </c>
+      <c r="B31" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" s="43" t="s">
+        <v>463</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>462</v>
+      </c>
+      <c r="F31" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" s="43" t="s">
+        <v>411</v>
+      </c>
+      <c r="H31" s="44">
+        <v>46255</v>
+      </c>
+      <c r="I31" s="44">
+        <v>46262</v>
+      </c>
+      <c r="J31" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K31" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L31" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M31" s="43" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="31.2">
+      <c r="A32" s="43" t="s">
+        <v>465</v>
+      </c>
+      <c r="B32" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D32" s="43" t="s">
+        <v>466</v>
+      </c>
+      <c r="E32" s="43" t="s">
+        <v>465</v>
+      </c>
+      <c r="F32" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" s="43" t="s">
+        <v>423</v>
+      </c>
+      <c r="H32" s="44">
+        <v>46255</v>
+      </c>
+      <c r="I32" s="44">
+        <v>46262</v>
+      </c>
+      <c r="J32" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K32" s="43" t="s">
+        <v>423</v>
+      </c>
+      <c r="L32" s="43" t="s">
+        <v>424</v>
+      </c>
+      <c r="M32" s="43" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="31.2">
+      <c r="A33" s="43" t="s">
+        <v>468</v>
+      </c>
+      <c r="B33" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" s="43" t="s">
+        <v>469</v>
+      </c>
+      <c r="E33" s="43" t="s">
+        <v>468</v>
+      </c>
+      <c r="F33" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" s="43" t="s">
+        <v>411</v>
+      </c>
+      <c r="H33" s="44">
+        <v>46258</v>
+      </c>
+      <c r="I33" s="44">
+        <v>46269</v>
+      </c>
+      <c r="J33" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K33" s="43"/>
+      <c r="L33" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M33" s="43" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="31.2">
+      <c r="A34" s="43" t="s">
+        <v>471</v>
+      </c>
+      <c r="B34" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" s="43" t="s">
+        <v>472</v>
+      </c>
+      <c r="E34" s="43" t="s">
+        <v>471</v>
+      </c>
+      <c r="F34" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="H34" s="44">
+        <v>46258</v>
+      </c>
+      <c r="I34" s="44">
+        <v>46269</v>
+      </c>
+      <c r="J34" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K34" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L34" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M34" s="43" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="31.2">
+      <c r="A35" s="43" t="s">
+        <v>474</v>
+      </c>
+      <c r="B35" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" s="43" t="s">
+        <v>475</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>474</v>
+      </c>
+      <c r="F35" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G35" s="43" t="s">
+        <v>476</v>
+      </c>
+      <c r="H35" s="44">
+        <v>46258</v>
+      </c>
+      <c r="I35" s="44">
+        <v>46269</v>
+      </c>
+      <c r="J35" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K35" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L35" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M35" s="43" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="31.2">
+      <c r="A36" s="43" t="s">
+        <v>478</v>
+      </c>
+      <c r="B36" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" s="43" t="s">
+        <v>479</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>478</v>
+      </c>
+      <c r="F36" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="H36" s="44">
+        <v>46262</v>
+      </c>
+      <c r="I36" s="44">
+        <v>46269</v>
+      </c>
+      <c r="J36" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K36" s="43"/>
+      <c r="L36" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M36" s="43" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="31.2">
+      <c r="A37" s="43" t="s">
+        <v>481</v>
+      </c>
+      <c r="B37" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" s="43" t="s">
+        <v>482</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>481</v>
+      </c>
+      <c r="F37" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" s="43"/>
+      <c r="H37" s="44">
+        <v>46269</v>
+      </c>
+      <c r="I37" s="44">
+        <v>46276</v>
+      </c>
+      <c r="J37" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K37" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L37" s="43" t="s">
+        <v>483</v>
+      </c>
+      <c r="M37" s="43" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="31.2">
+      <c r="A38" s="43" t="s">
+        <v>485</v>
+      </c>
+      <c r="B38" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" s="43" t="s">
+        <v>486</v>
+      </c>
+      <c r="E38" s="43" t="s">
+        <v>485</v>
+      </c>
+      <c r="F38" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38" s="43" t="s">
+        <v>411</v>
+      </c>
+      <c r="H38" s="44">
+        <v>46269</v>
+      </c>
+      <c r="I38" s="44">
+        <v>46276</v>
+      </c>
+      <c r="J38" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K38" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L38" s="43" t="s">
+        <v>483</v>
+      </c>
+      <c r="M38" s="43" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="31.2">
+      <c r="A39" s="43" t="s">
+        <v>488</v>
+      </c>
+      <c r="B39" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="43" t="s">
+        <v>489</v>
+      </c>
+      <c r="E39" s="43" t="s">
+        <v>488</v>
+      </c>
+      <c r="F39" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="H39" s="44">
+        <v>46273</v>
+      </c>
+      <c r="I39" s="44">
+        <v>46276</v>
+      </c>
+      <c r="J39" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K39" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L39" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M39" s="43" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="31.2">
+      <c r="A40" s="43" t="s">
+        <v>491</v>
+      </c>
+      <c r="B40" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" s="43" t="s">
+        <v>492</v>
+      </c>
+      <c r="E40" s="43" t="s">
+        <v>491</v>
+      </c>
+      <c r="F40" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" s="43"/>
+      <c r="H40" s="44">
+        <v>46273</v>
+      </c>
+      <c r="I40" s="44">
+        <v>46276</v>
+      </c>
+      <c r="J40" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K40" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L40" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M40" s="43" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="31.2">
+      <c r="A41" s="43" t="s">
+        <v>494</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" s="43" t="s">
+        <v>495</v>
+      </c>
+      <c r="E41" s="43" t="s">
+        <v>494</v>
+      </c>
+      <c r="F41" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="43" t="s">
+        <v>496</v>
+      </c>
+      <c r="H41" s="44">
+        <v>46273</v>
+      </c>
+      <c r="I41" s="44">
+        <v>46276</v>
+      </c>
+      <c r="J41" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K41" s="43" t="s">
+        <v>496</v>
+      </c>
+      <c r="L41" s="43" t="s">
+        <v>483</v>
+      </c>
+      <c r="M41" s="43" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="31.2">
+      <c r="A42" s="43" t="s">
+        <v>498</v>
+      </c>
+      <c r="B42" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="43" t="s">
+        <v>499</v>
+      </c>
+      <c r="E42" s="43" t="s">
+        <v>498</v>
+      </c>
+      <c r="F42" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G5" s="4">
-        <v>46182</v>
-      </c>
-      <c r="H5" s="4">
-        <v>46185</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="G42" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="H42" s="44">
+        <v>46269</v>
+      </c>
+      <c r="I42" s="44">
+        <v>46283</v>
+      </c>
+      <c r="J42" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K42" s="43" t="s">
+        <v>536</v>
+      </c>
+      <c r="L42" s="43" t="s">
+        <v>446</v>
+      </c>
+      <c r="M42" s="43" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="31.2">
+      <c r="A43" s="43" t="s">
+        <v>501</v>
+      </c>
+      <c r="B43" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="D43" s="43" t="s">
+        <v>502</v>
+      </c>
+      <c r="E43" s="43" t="s">
+        <v>501</v>
+      </c>
+      <c r="F43" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="G43" s="43" t="s">
+        <v>503</v>
+      </c>
+      <c r="H43" s="44">
+        <v>46273</v>
+      </c>
+      <c r="I43" s="44">
+        <v>46283</v>
+      </c>
+      <c r="J43" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K43" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" hidden="1">
-      <c r="A6" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="L43" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="M43" s="43" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="31.2">
+      <c r="A44" s="43" t="s">
+        <v>505</v>
+      </c>
+      <c r="B44" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" s="43" t="s">
+        <v>506</v>
+      </c>
+      <c r="E44" s="43" t="s">
+        <v>505</v>
+      </c>
+      <c r="F44" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" s="43" t="s">
+        <v>496</v>
+      </c>
+      <c r="H44" s="44">
+        <v>46273</v>
+      </c>
+      <c r="I44" s="44">
+        <v>46283</v>
+      </c>
+      <c r="J44" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K44" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L44" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="M44" s="43" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="31.2">
+      <c r="A45" s="43" t="s">
+        <v>508</v>
+      </c>
+      <c r="B45" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" s="43" t="s">
+        <v>509</v>
+      </c>
+      <c r="E45" s="43" t="s">
+        <v>508</v>
+      </c>
+      <c r="F45" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G45" s="43" t="s">
+        <v>544</v>
+      </c>
+      <c r="H45" s="44">
+        <v>46277</v>
+      </c>
+      <c r="I45" s="44">
+        <v>46283</v>
+      </c>
+      <c r="J45" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K45" s="43" t="s">
+        <v>543</v>
+      </c>
+      <c r="L45" s="43" t="s">
+        <v>510</v>
+      </c>
+      <c r="M45" s="43" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="31.2">
+      <c r="A46" s="43" t="s">
+        <v>512</v>
+      </c>
+      <c r="B46" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" s="43" t="s">
+        <v>513</v>
+      </c>
+      <c r="E46" s="43" t="s">
+        <v>512</v>
+      </c>
+      <c r="F46" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="G46" s="43" t="s">
+        <v>503</v>
+      </c>
+      <c r="H46" s="44">
+        <v>46280</v>
+      </c>
+      <c r="I46" s="44">
+        <v>46283</v>
+      </c>
+      <c r="J46" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="K46" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="4">
-        <v>46182</v>
-      </c>
-      <c r="H6" s="4">
-        <v>46185</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" hidden="1">
-      <c r="A7" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G7" s="4">
-        <v>46179</v>
-      </c>
-      <c r="H7" s="4">
-        <v>46185</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" hidden="1">
-      <c r="A8" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G8" s="4">
-        <v>46179</v>
-      </c>
-      <c r="H8" s="4">
-        <v>46185</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" hidden="1">
-      <c r="A9" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G9" s="4">
-        <v>46183</v>
-      </c>
-      <c r="H9" s="4">
-        <v>46185</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" hidden="1">
-      <c r="A10" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="G10" s="4">
-        <v>46209</v>
-      </c>
-      <c r="H10" s="4">
-        <v>46215</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" hidden="1">
-      <c r="A11" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="G11" s="4">
-        <v>46209</v>
-      </c>
-      <c r="H11" s="4">
-        <v>46215</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" hidden="1">
-      <c r="A12" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="G12" s="4">
-        <v>46209</v>
-      </c>
-      <c r="H12" s="4">
-        <v>46215</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" hidden="1">
-      <c r="A13" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="G13" s="4">
-        <v>46209</v>
-      </c>
-      <c r="H13" s="4">
-        <v>46215</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" hidden="1">
-      <c r="A14" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="G14" s="4">
-        <v>46191</v>
-      </c>
-      <c r="H14" s="4">
-        <v>46198</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" hidden="1">
-      <c r="A15" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="G15" s="4">
-        <v>46191</v>
-      </c>
-      <c r="H15" s="4">
-        <v>46198</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" hidden="1">
-      <c r="A16" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G16" s="4">
-        <v>46191</v>
-      </c>
-      <c r="H16" s="4">
-        <v>46198</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" hidden="1">
-      <c r="A17" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G17" s="4">
-        <v>46191</v>
-      </c>
-      <c r="H17" s="4">
-        <v>46198</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" hidden="1">
-      <c r="A18" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="G18" s="4">
-        <v>46191</v>
-      </c>
-      <c r="H18" s="4">
-        <v>46198</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" hidden="1">
-      <c r="A19" s="2" t="s">
+      <c r="L46" s="43" t="s">
         <v>428</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G19" s="4">
-        <v>46191</v>
-      </c>
-      <c r="H19" s="4">
-        <v>46198</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" hidden="1">
-      <c r="A20" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G20" s="4">
-        <v>46191</v>
-      </c>
-      <c r="H20" s="4">
-        <v>46198</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" hidden="1">
-      <c r="A21" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="G21" s="4">
-        <v>46191</v>
-      </c>
-      <c r="H21" s="4">
-        <v>46198</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" hidden="1">
-      <c r="A22" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="G22" s="4">
-        <v>46248</v>
-      </c>
-      <c r="H22" s="4">
-        <v>46262</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" hidden="1">
-      <c r="A23" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G23" s="4">
-        <v>46251</v>
-      </c>
-      <c r="H23" s="4">
-        <v>46262</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" hidden="1">
-      <c r="A24" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="G24" s="4">
-        <v>46248</v>
-      </c>
-      <c r="H24" s="4">
-        <v>46262</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="G25" s="4">
-        <v>46255</v>
-      </c>
-      <c r="H25" s="4">
-        <v>46262</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" hidden="1">
-      <c r="A26" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G26" s="4">
-        <v>46251</v>
-      </c>
-      <c r="H26" s="4">
-        <v>46262</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" hidden="1">
-      <c r="A27" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G27" s="4">
-        <v>46251</v>
-      </c>
-      <c r="H27" s="4">
-        <v>46262</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" hidden="1">
-      <c r="A28" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G28" s="4">
-        <v>46255</v>
-      </c>
-      <c r="H28" s="4">
-        <v>46262</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" hidden="1">
-      <c r="A29" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G29" s="4">
-        <v>46255</v>
-      </c>
-      <c r="H29" s="4">
-        <v>46262</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="G30" s="4">
-        <v>46255</v>
-      </c>
-      <c r="H30" s="4">
-        <v>46262</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" hidden="1">
-      <c r="A31" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="G31" s="4">
-        <v>46255</v>
-      </c>
-      <c r="H31" s="4">
-        <v>46262</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" hidden="1">
-      <c r="A32" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="G32" s="4">
-        <v>46255</v>
-      </c>
-      <c r="H32" s="4">
-        <v>46262</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" hidden="1">
-      <c r="A33" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="G33" s="4">
-        <v>46258</v>
-      </c>
-      <c r="H33" s="4">
-        <v>46269</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" hidden="1">
-      <c r="A34" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G34" s="4">
-        <v>46258</v>
-      </c>
-      <c r="H34" s="4">
-        <v>46269</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" hidden="1">
-      <c r="A35" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="G35" s="4">
-        <v>46258</v>
-      </c>
-      <c r="H35" s="4">
-        <v>46269</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" hidden="1">
-      <c r="A36" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G36" s="4">
-        <v>46262</v>
-      </c>
-      <c r="H36" s="4">
-        <v>46269</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" hidden="1">
-      <c r="A37" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="G37" s="4">
-        <v>46269</v>
-      </c>
-      <c r="H37" s="4">
-        <v>46276</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" hidden="1">
-      <c r="A38" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="G38" s="4">
-        <v>46269</v>
-      </c>
-      <c r="H38" s="4">
-        <v>46276</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" hidden="1">
-      <c r="A39" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G39" s="4">
-        <v>46273</v>
-      </c>
-      <c r="H39" s="4">
-        <v>46276</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" hidden="1">
-      <c r="A40" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="G40" s="4">
-        <v>46273</v>
-      </c>
-      <c r="H40" s="4">
-        <v>46276</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="26.4">
-      <c r="A41" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="G41" s="4">
-        <v>46273</v>
-      </c>
-      <c r="H41" s="4">
-        <v>46276</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
-      <c r="A42" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G42" s="4">
-        <v>46269</v>
-      </c>
-      <c r="H42" s="4">
-        <v>46283</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" hidden="1">
-      <c r="A43" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="G43" s="4">
-        <v>46273</v>
-      </c>
-      <c r="H43" s="4">
-        <v>46283</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="A44" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="G44" s="4">
-        <v>46273</v>
-      </c>
-      <c r="H44" s="4">
-        <v>46283</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" hidden="1">
-      <c r="A45" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="G45" s="4">
-        <v>46277</v>
-      </c>
-      <c r="H45" s="4">
-        <v>46283</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" hidden="1">
-      <c r="A46" s="2" t="s">
+      <c r="M46" s="43" t="s">
         <v>514</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="G46" s="4">
-        <v>46280</v>
-      </c>
-      <c r="H46" s="4">
-        <v>46283</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>516</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="I5:I46" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" sqref="J5:J46" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Done,Deferred"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6113,1977 +6539,2524 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:AA40"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.19921875" style="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5" style="20" customWidth="1"/>
-    <col min="3" max="3" width="32.8984375" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.09765625" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.8984375" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.5" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5" style="20" customWidth="1"/>
-    <col min="11" max="11" width="4.796875" style="20" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="12" style="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.8984375" style="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.69921875" style="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.8984375" style="20" hidden="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.69921875" style="20"/>
+    <col min="1" max="1" width="7.19921875" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5" style="18" customWidth="1"/>
+    <col min="3" max="3" width="32.8984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.69921875" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.09765625" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.09765625" style="18" customWidth="1"/>
+    <col min="7" max="7" width="17.69921875" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.8984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.796875" style="18" customWidth="1"/>
+    <col min="11" max="11" width="13.5" style="18" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18" style="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5" style="18" customWidth="1"/>
+    <col min="14" max="14" width="4.796875" style="18" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="12" style="18" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.8984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.69921875" style="18" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.8984375" style="18" hidden="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.69921875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="36">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:27" ht="36">
+      <c r="A1" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="16" t="s">
+        <v>581</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>582</v>
+      </c>
+      <c r="H1" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="I1" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="J1" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="K1" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="L1" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="M1" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="N1" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="O1" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="P1" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="Q1" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="R1" s="17" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="36" hidden="1">
-      <c r="A2" s="21" t="s">
+      <c r="T1" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="U1" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="V1" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="W1" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="X1" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y1" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z1" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA1" s="18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="36">
+      <c r="A2" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="F2" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="H2" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="I2" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="43">
+      <c r="J2" s="41">
         <v>46174</v>
       </c>
-      <c r="H2" s="43">
+      <c r="K2" s="41">
         <v>46177</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="L2" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="M2" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="N2" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="O2" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M2" s="22" t="s">
+      <c r="P2" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="N2" s="22" t="s">
+      <c r="Q2" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="O2" s="23" t="str">
-        <f t="shared" ref="O2:O40" ca="1" si="0">IF(J2="Done","Closed",IF(H2&lt;TODAY(),"Overdue",IF(H2-TODAY()&lt;=7,"Due &lt;=7d","On Track")))</f>
+      <c r="R2" s="21" t="str">
+        <f t="shared" ref="R2:R40" ca="1" si="0">IF(M2="Done","Closed",IF(K2&lt;TODAY(),"Overdue",IF(K2-TODAY()&lt;=7,"Due &lt;=7d","On Track")))</f>
         <v>Overdue</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="36" hidden="1">
-      <c r="A3" s="21" t="s">
+      <c r="T2" s="18" t="str" cm="1">
+        <f t="array" ref="T2:T6">_xlfn._xlws.FILTER('Deliverable Control'!$D$5:$D$46,'Deliverable Control'!$C$5:$C$46='Detailed Task Tracker'!T1,"XXX")</f>
+        <v>AMS 2.0 Transformation Charter</v>
+      </c>
+      <c r="U2" s="18" t="str" cm="1">
+        <f t="array" ref="U2:U5">_xlfn._xlws.FILTER('Deliverable Control'!$D$5:$D$46,'Deliverable Control'!$C$5:$C$46='Detailed Task Tracker'!U1,"XXX")</f>
+        <v>Current-State Assessment Summary</v>
+      </c>
+      <c r="V2" s="18" t="str" cm="1">
+        <f t="array" ref="V2:V9">_xlfn._xlws.FILTER('Deliverable Control'!$D$5:$D$46,'Deliverable Control'!$C$5:$C$46='Detailed Task Tracker'!V1,"XXX")</f>
+        <v>AMS Application Support Inventory</v>
+      </c>
+      <c r="W2" s="18" t="str" cm="1">
+        <f t="array" ref="W2:W5">_xlfn._xlws.FILTER('Deliverable Control'!$D$5:$D$46,'Deliverable Control'!$C$5:$C$46='Detailed Task Tracker'!W1,"XXX")</f>
+        <v>AMS RACI Matrix</v>
+      </c>
+      <c r="X2" s="18" t="str" cm="1">
+        <f t="array" ref="X2:X8">_xlfn._xlws.FILTER('Deliverable Control'!$D$5:$D$46,'Deliverable Control'!$C$5:$C$46='Detailed Task Tracker'!X1,"XXX")</f>
+        <v>Future-State Governance Calendar</v>
+      </c>
+      <c r="Y2" s="18" t="str" cm="1">
+        <f t="array" ref="Y2:Y5">_xlfn._xlws.FILTER('Deliverable Control'!$D$5:$D$46,'Deliverable Control'!$C$5:$C$46='Detailed Task Tracker'!Y1,"XXX")</f>
+        <v>Capacity and Demand Model</v>
+      </c>
+      <c r="Z2" s="18" t="str" cm="1">
+        <f t="array" ref="Z2:Z6">_xlfn._xlws.FILTER('Deliverable Control'!$D$5:$D$46,'Deliverable Control'!$C$5:$C$46='Detailed Task Tracker'!Z1,"XXX")</f>
+        <v>AMS 2.0 Transformation Roadmap</v>
+      </c>
+      <c r="AA2" s="18" t="str" cm="1">
+        <f t="array" ref="AA2:AA6">_xlfn._xlws.FILTER('Deliverable Control'!$D$5:$D$46,'Deliverable Control'!$C$5:$C$46='Detailed Task Tracker'!AA1,"XXX")</f>
+        <v>Automation Maturity Assessment Summary</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="36">
+      <c r="A3" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="F3" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="H3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="I3" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="G3" s="43">
+      <c r="J3" s="41">
         <v>46176</v>
       </c>
-      <c r="H3" s="43">
+      <c r="K3" s="41">
         <v>46183</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="L3" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="M3" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="N3" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="O3" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="P3" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="Q3" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="O3" s="23" t="str">
+      <c r="R3" s="21" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Overdue</v>
+      </c>
+      <c r="T3" s="18" t="str">
+        <v>Integrated Project Plan</v>
+      </c>
+      <c r="U3" s="18" t="str">
+        <v>Current-State Operating View</v>
+      </c>
+      <c r="V3" s="18" t="str">
+        <v>Application Ownership Matrix</v>
+      </c>
+      <c r="W3" s="18" t="str">
+        <v>Target Role Profiles</v>
+      </c>
+      <c r="X3" s="18" t="str">
+        <v>Meeting Rationalization Recommendations</v>
+      </c>
+      <c r="Y3" s="18" t="str">
+        <v>Capacity Heatmap</v>
+      </c>
+      <c r="Z3" s="18" t="str">
+        <v>Implementation Backlog</v>
+      </c>
+      <c r="AA3" s="18" t="str">
+        <v>AI and Automation Opportunity Map</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="36">
+      <c r="A4" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="J4" s="41">
+        <v>46176</v>
+      </c>
+      <c r="K4" s="41">
+        <v>46179</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="M4" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="N4" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="O4" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="P4" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q4" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="R4" s="21" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Overdue</v>
+      </c>
+      <c r="T4" s="18" t="str">
+        <v>Data Request / Discovery Tracker</v>
+      </c>
+      <c r="U4" s="18" t="str">
+        <v>Pain Point and Opportunity Register</v>
+      </c>
+      <c r="V4" s="18" t="str">
+        <v>ServiceNow Queue / Assignment Group Inventory</v>
+      </c>
+      <c r="W4" s="18" t="str">
+        <v>Role Gap and Overlap Analysis</v>
+      </c>
+      <c r="X4" s="18" t="str">
+        <v>Governance Templates</v>
+      </c>
+      <c r="Y4" s="18" t="str">
+        <v>Role / Demand Alignment View</v>
+      </c>
+      <c r="Z4" s="18" t="str">
+        <v>Quick Win Execution Support Plan</v>
+      </c>
+      <c r="AA4" s="18" t="str">
+        <v>Prioritized Automation Recommendations</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="36">
+      <c r="A5" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="J5" s="41">
+        <v>46177</v>
+      </c>
+      <c r="K5" s="41">
+        <v>46182</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="M5" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="N5" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="O5" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="P5" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q5" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="R5" s="21" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Overdue</v>
+      </c>
+      <c r="T5" s="18" t="str">
+        <v>RAID / Action Log</v>
+      </c>
+      <c r="U5" s="18" t="str">
+        <v>Quick Win Recommendations</v>
+      </c>
+      <c r="V5" s="18" t="str">
+        <v>Queue-to-App-to-Owner Mapping</v>
+      </c>
+      <c r="W5" s="18" t="str">
+        <v>AMS 2.0 Operating Model Recommendations</v>
+      </c>
+      <c r="X5" s="18" t="str">
+        <v>Communication Charter</v>
+      </c>
+      <c r="Y5" s="18" t="str">
+        <v>Capacity Recommendations</v>
+      </c>
+      <c r="Z5" s="18" t="str">
+        <v>Executive Readout Deck</v>
+      </c>
+      <c r="AA5" s="18" t="str">
+        <v>Agentic AI Infusion and Intervention Inputs</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="36">
+      <c r="A6" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="J6" s="41">
+        <v>46177</v>
+      </c>
+      <c r="K6" s="41">
+        <v>46182</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="O6" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="P6" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q6" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="R6" s="21" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Overdue</v>
+      </c>
+      <c r="T6" s="18" t="str">
+        <v>Weekly Status Update Template</v>
+      </c>
+      <c r="V6" s="18" t="str">
+        <v>Dashboard and Reporting Inventory</v>
+      </c>
+      <c r="X6" s="18" t="str">
+        <v>AMS KPI Framework</v>
+      </c>
+      <c r="Z6" s="18" t="str">
+        <v>Final Handover Package</v>
+      </c>
+      <c r="AA6" s="18" t="str">
+        <v>Automation Assumptions and Dependencies Register</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="36">
+      <c r="A7" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="J7" s="41">
+        <v>46178</v>
+      </c>
+      <c r="K7" s="41">
+        <v>46183</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="M7" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="N7" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="O7" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="P7" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q7" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="R7" s="21" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Overdue</v>
+      </c>
+      <c r="V7" s="18" t="str">
+        <v>Governance and Meeting Inventory</v>
+      </c>
+      <c r="X7" s="18" t="str">
+        <v>Executive AMS Scorecard Template</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="36">
+      <c r="A8" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="J8" s="41">
+        <v>46178</v>
+      </c>
+      <c r="K8" s="41">
+        <v>46184</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="N8" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="O8" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="P8" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q8" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="R8" s="21" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Overdue</v>
+      </c>
+      <c r="V8" s="18" t="str">
+        <v>Stakeholder Map</v>
+      </c>
+      <c r="X8" s="18" t="str">
+        <v>Operational Dashboard Requirements</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="36">
+      <c r="A9" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="J9" s="41">
+        <v>46176</v>
+      </c>
+      <c r="K9" s="41">
+        <v>46179</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="N9" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="O9" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="P9" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q9" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="R9" s="21" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Overdue</v>
+      </c>
+      <c r="V9" s="18" t="str">
+        <v>Mondelez AMS Team Profile Inventory</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="36">
+      <c r="A10" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="J10" s="41">
+        <v>46188</v>
+      </c>
+      <c r="K10" s="41">
+        <v>46190</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="M10" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="N10" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="O10" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="P10" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q10" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="R10" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Due &lt;=7d</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="36" hidden="1">
-      <c r="A4" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="G4" s="43">
-        <v>46176</v>
-      </c>
-      <c r="H4" s="43">
-        <v>46179</v>
-      </c>
-      <c r="I4" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="J4" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="K4" s="22" t="s">
+    <row r="11" spans="1:27" ht="54">
+      <c r="A11" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="J11" s="41">
+        <v>46189</v>
+      </c>
+      <c r="K11" s="41">
+        <v>46199</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="M11" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="N11" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L4" s="22" t="s">
+      <c r="O11" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M4" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="N4" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="O4" s="23" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Overdue</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="36">
-      <c r="A5" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G5" s="43">
-        <v>46177</v>
-      </c>
-      <c r="H5" s="43">
-        <v>46182</v>
-      </c>
-      <c r="I5" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="J5" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="M5" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="N5" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="O5" s="23" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Due &lt;=7d</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="36" hidden="1">
-      <c r="A6" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="G6" s="43">
-        <v>46177</v>
-      </c>
-      <c r="H6" s="43">
-        <v>46182</v>
-      </c>
-      <c r="I6" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="J6" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="M6" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="N6" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="O6" s="23" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Due &lt;=7d</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="36" hidden="1">
-      <c r="A7" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="G7" s="43">
-        <v>46178</v>
-      </c>
-      <c r="H7" s="43">
-        <v>46183</v>
-      </c>
-      <c r="I7" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="J7" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="M7" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="N7" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="O7" s="23" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Due &lt;=7d</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="36" hidden="1">
-      <c r="A8" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="G8" s="43">
-        <v>46178</v>
-      </c>
-      <c r="H8" s="43">
-        <v>46184</v>
-      </c>
-      <c r="I8" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J8" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="M8" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="N8" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="O8" s="23" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Due &lt;=7d</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="36" hidden="1">
-      <c r="A9" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="G9" s="43">
-        <v>46176</v>
-      </c>
-      <c r="H9" s="43">
-        <v>46179</v>
-      </c>
-      <c r="I9" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="J9" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="M9" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="N9" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="O9" s="23" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Overdue</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="36" hidden="1">
-      <c r="A10" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="G10" s="43">
-        <v>46188</v>
-      </c>
-      <c r="H10" s="43">
-        <v>46190</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="J10" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="L10" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="M10" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="N10" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="O10" s="23" t="str">
+      <c r="P11" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q11" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="R11" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="54" hidden="1">
-      <c r="A11" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="B11" s="22" t="s">
+    <row r="12" spans="1:27" ht="36">
+      <c r="A12" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B12" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C12" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="D11" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="G11" s="43">
-        <v>46189</v>
-      </c>
-      <c r="H11" s="43">
-        <v>46199</v>
-      </c>
-      <c r="I11" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="J11" s="22" t="s">
+      <c r="D12" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="J12" s="41">
+        <v>46190</v>
+      </c>
+      <c r="K12" s="41">
+        <v>46206</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="M12" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K11" s="22" t="s">
+      <c r="N12" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L11" s="22" t="s">
+      <c r="O12" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M11" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="N11" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="O11" s="23" t="str">
+      <c r="P12" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q12" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="R12" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="36" hidden="1">
-      <c r="A12" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="B12" s="22" t="s">
+    <row r="13" spans="1:27" ht="36">
+      <c r="A13" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="B13" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="G12" s="43">
+      <c r="C13" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="J13" s="41">
         <v>46190</v>
       </c>
-      <c r="H12" s="43">
-        <v>46206</v>
-      </c>
-      <c r="I12" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="J12" s="22" t="s">
+      <c r="K13" s="41">
+        <v>46204</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="M13" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K12" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="L12" s="22" t="s">
+      <c r="N13" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="O13" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M12" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="N12" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="O12" s="23" t="str">
+      <c r="P13" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q13" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="R13" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="36" hidden="1">
-      <c r="A13" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="B13" s="22" t="s">
+    <row r="14" spans="1:27" ht="36">
+      <c r="A14" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C14" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="D13" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="G13" s="43">
+      <c r="D14" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="J14" s="41">
         <v>46190</v>
       </c>
-      <c r="H13" s="43">
+      <c r="K14" s="41">
         <v>46204</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="L14" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="M14" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K13" s="22" t="s">
+      <c r="N14" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="L13" s="22" t="s">
+      <c r="O14" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M13" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="N13" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="O13" s="23" t="str">
+      <c r="P14" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q14" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="R14" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="36">
-      <c r="A14" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="B14" s="22" t="s">
+    <row r="15" spans="1:27" ht="54">
+      <c r="A15" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C15" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="D14" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E14" s="22" t="s">
+      <c r="D15" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="H15" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="G14" s="43">
-        <v>46190</v>
-      </c>
-      <c r="H14" s="43">
-        <v>46204</v>
-      </c>
-      <c r="I14" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="J14" s="22" t="s">
+      <c r="I15" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="J15" s="41">
+        <v>46192</v>
+      </c>
+      <c r="K15" s="41">
+        <v>46207</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="M15" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K14" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="L14" s="22" t="s">
+      <c r="N15" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="O15" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M14" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="N14" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="O14" s="23" t="str">
+      <c r="P15" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q15" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="R15" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="54">
-      <c r="A15" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="B15" s="22" t="s">
+    <row r="16" spans="1:27" ht="36">
+      <c r="A16" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="B16" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C15" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="G15" s="43">
-        <v>46192</v>
-      </c>
-      <c r="H15" s="43">
-        <v>46207</v>
-      </c>
-      <c r="I15" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="J15" s="22" t="s">
+      <c r="C16" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="J16" s="41">
+        <v>46196</v>
+      </c>
+      <c r="K16" s="41">
+        <v>46213</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="M16" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K15" s="22" t="s">
+      <c r="N16" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L15" s="22" t="s">
+      <c r="O16" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M15" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="N15" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="O15" s="23" t="str">
+      <c r="P16" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q16" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="R16" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="36" hidden="1">
-      <c r="A16" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="B16" s="22" t="s">
+    <row r="17" spans="1:18" ht="36">
+      <c r="A17" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="B17" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C16" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="G16" s="43">
-        <v>46196</v>
-      </c>
-      <c r="H16" s="43">
-        <v>46213</v>
-      </c>
-      <c r="I16" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="J16" s="22" t="s">
+      <c r="C17" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>418</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="J17" s="41">
+        <v>46197</v>
+      </c>
+      <c r="K17" s="41">
+        <v>46211</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="M17" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K16" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="L16" s="22" t="s">
+      <c r="N17" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="O17" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M16" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="N16" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="O16" s="23" t="str">
+      <c r="P17" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q17" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="R17" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="36" hidden="1">
-      <c r="A17" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="B17" s="22" t="s">
+    <row r="18" spans="1:18" ht="36">
+      <c r="A18" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B18" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C18" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="D17" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="G17" s="43">
+      <c r="D18" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>418</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="J18" s="41">
         <v>46197</v>
       </c>
-      <c r="H17" s="43">
+      <c r="K18" s="41">
         <v>46211</v>
       </c>
-      <c r="I17" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="J17" s="22" t="s">
+      <c r="L18" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="M18" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K17" s="22" t="s">
+      <c r="N18" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="L17" s="22" t="s">
+      <c r="O18" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M17" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="N17" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="O17" s="23" t="str">
+      <c r="P18" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q18" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="R18" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="36">
-      <c r="A18" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="B18" s="22" t="s">
+    <row r="19" spans="1:18" ht="36">
+      <c r="A19" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="B19" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="G18" s="43">
+      <c r="C19" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="J19" s="41">
         <v>46197</v>
       </c>
-      <c r="H18" s="43">
-        <v>46211</v>
-      </c>
-      <c r="I18" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="J18" s="22" t="s">
+      <c r="K19" s="41">
+        <v>46213</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="M19" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K18" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="L18" s="22" t="s">
+      <c r="N19" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="O19" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M18" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="N18" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="O18" s="23" t="str">
+      <c r="P19" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q19" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="R19" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="36" hidden="1">
-      <c r="A19" s="21" t="s">
-        <v>235</v>
-      </c>
-      <c r="B19" s="22" t="s">
+    <row r="20" spans="1:18" ht="36">
+      <c r="A20" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="B20" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="G19" s="43">
-        <v>46197</v>
-      </c>
-      <c r="H19" s="43">
-        <v>46213</v>
-      </c>
-      <c r="I19" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="J19" s="22" t="s">
+      <c r="C20" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="J20" s="41">
+        <v>46204</v>
+      </c>
+      <c r="K20" s="41">
+        <v>46218</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="M20" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K19" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="L19" s="22" t="s">
+      <c r="N20" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="O20" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M19" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="N19" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="O19" s="23" t="str">
+      <c r="P20" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q20" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="R20" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="36">
-      <c r="A20" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="B20" s="22" t="s">
+    <row r="21" spans="1:18" ht="36">
+      <c r="A21" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="B21" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C20" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="G20" s="43">
-        <v>46204</v>
-      </c>
-      <c r="H20" s="43">
-        <v>46218</v>
-      </c>
-      <c r="I20" s="22" t="s">
-        <v>246</v>
-      </c>
-      <c r="J20" s="22" t="s">
+      <c r="C21" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="J21" s="41">
+        <v>46211</v>
+      </c>
+      <c r="K21" s="41">
+        <v>46220</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="M21" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K20" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="L20" s="22" t="s">
+      <c r="N21" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="O21" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M20" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="N20" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="O20" s="23" t="str">
+      <c r="P21" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q21" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="R21" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="36" hidden="1">
-      <c r="A21" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="B21" s="22" t="s">
+    <row r="22" spans="1:18" ht="36">
+      <c r="A22" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C22" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="D21" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="E21" s="22" t="s">
+      <c r="D22" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="H22" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="G21" s="43">
-        <v>46211</v>
-      </c>
-      <c r="H21" s="43">
-        <v>46220</v>
-      </c>
-      <c r="I21" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="J21" s="22" t="s">
+      <c r="I22" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="J22" s="41">
+        <v>46224</v>
+      </c>
+      <c r="K22" s="41">
+        <v>46226</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="M22" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K21" s="22" t="s">
+      <c r="N22" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L21" s="22" t="s">
+      <c r="O22" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M21" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="N21" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="O21" s="23" t="str">
+      <c r="P22" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q22" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="R22" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="36" hidden="1">
-      <c r="A22" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="B22" s="22" t="s">
+    <row r="23" spans="1:18" ht="36">
+      <c r="A23" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="B23" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C23" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="D22" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="G22" s="43">
-        <v>46224</v>
-      </c>
-      <c r="H22" s="43">
-        <v>46226</v>
-      </c>
-      <c r="I22" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="J22" s="22" t="s">
+      <c r="D23" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="J23" s="41">
+        <v>46225</v>
+      </c>
+      <c r="K23" s="41">
+        <v>46227</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="M23" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K22" s="22" t="s">
+      <c r="N23" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L22" s="22" t="s">
+      <c r="O23" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M22" s="22" t="s">
-        <v>259</v>
-      </c>
-      <c r="N22" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="O22" s="23" t="str">
+      <c r="P23" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q23" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="R23" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="36" hidden="1">
-      <c r="A23" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>262</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="G23" s="43">
-        <v>46225</v>
-      </c>
-      <c r="H23" s="43">
-        <v>46227</v>
-      </c>
-      <c r="I23" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="J23" s="22" t="s">
+    <row r="24" spans="1:18" ht="36">
+      <c r="A24" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="J24" s="41">
+        <v>46230</v>
+      </c>
+      <c r="K24" s="41">
+        <v>46239</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="M24" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K23" s="22" t="s">
+      <c r="N24" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L23" s="22" t="s">
+      <c r="O24" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M23" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="N23" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="O23" s="23" t="str">
+      <c r="P24" s="20" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q24" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="R24" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="36" hidden="1">
-      <c r="A24" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="B24" s="22" t="s">
+    <row r="25" spans="1:18" ht="36">
+      <c r="A25" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="B25" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C25" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="D24" s="22" t="s">
-        <v>269</v>
-      </c>
-      <c r="E24" s="22" t="s">
+      <c r="D25" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="H25" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="G24" s="43">
-        <v>46230</v>
-      </c>
-      <c r="H24" s="43">
-        <v>46239</v>
-      </c>
-      <c r="I24" s="22" t="s">
-        <v>271</v>
-      </c>
-      <c r="J24" s="22" t="s">
+      <c r="I25" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="J25" s="41">
+        <v>46238</v>
+      </c>
+      <c r="K25" s="41">
+        <v>46240</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="M25" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K24" s="22" t="s">
+      <c r="N25" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L24" s="22" t="s">
+      <c r="O25" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M24" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="N24" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="O24" s="23" t="str">
+      <c r="P25" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q25" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="R25" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="36" hidden="1">
-      <c r="A25" s="21" t="s">
-        <v>274</v>
-      </c>
-      <c r="B25" s="22" t="s">
+    <row r="26" spans="1:18" ht="54">
+      <c r="A26" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="B26" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C25" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="G25" s="43">
-        <v>46238</v>
-      </c>
-      <c r="H25" s="43">
-        <v>46240</v>
-      </c>
-      <c r="I25" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="J25" s="22" t="s">
+      <c r="C26" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>447</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="J26" s="41">
+        <v>46237</v>
+      </c>
+      <c r="K26" s="41">
+        <v>46246</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="M26" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K25" s="22" t="s">
+      <c r="N26" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L25" s="22" t="s">
+      <c r="O26" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M25" s="22" t="s">
-        <v>278</v>
-      </c>
-      <c r="N25" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="O25" s="23" t="str">
+      <c r="P26" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q26" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="R26" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="54" hidden="1">
-      <c r="A26" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="B26" s="22" t="s">
+    <row r="27" spans="1:18" ht="36">
+      <c r="A27" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="B27" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C27" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="D26" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="E26" s="22" t="s">
+      <c r="D27" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>460</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>459</v>
+      </c>
+      <c r="H27" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="F26" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="G26" s="43">
-        <v>46237</v>
-      </c>
-      <c r="H26" s="43">
-        <v>46246</v>
-      </c>
-      <c r="I26" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="J26" s="22" t="s">
+      <c r="I27" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="J27" s="41">
+        <v>46240</v>
+      </c>
+      <c r="K27" s="41">
+        <v>46251</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="M27" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K26" s="22" t="s">
+      <c r="N27" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L26" s="22" t="s">
+      <c r="O27" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M26" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="N26" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="O26" s="23" t="str">
+      <c r="P27" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q27" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="R27" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="36" hidden="1">
-      <c r="A27" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="B27" s="22" t="s">
+    <row r="28" spans="1:18" ht="36">
+      <c r="A28" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="B28" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C27" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="G27" s="43">
-        <v>46240</v>
-      </c>
-      <c r="H27" s="43">
-        <v>46251</v>
-      </c>
-      <c r="I27" s="22" t="s">
-        <v>288</v>
-      </c>
-      <c r="J27" s="22" t="s">
+      <c r="C28" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>472</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>471</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="J28" s="41">
+        <v>46237</v>
+      </c>
+      <c r="K28" s="41">
+        <v>46254</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="M28" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K27" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="L27" s="22" t="s">
+      <c r="N28" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="O28" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M27" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="N27" s="22" t="s">
-        <v>290</v>
-      </c>
-      <c r="O27" s="23" t="str">
+      <c r="P28" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q28" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="R28" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="36">
-      <c r="A28" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="B28" s="22" t="s">
+    <row r="29" spans="1:18" ht="36">
+      <c r="A29" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="B29" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C28" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>292</v>
-      </c>
-      <c r="E28" s="22" t="s">
+      <c r="C29" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>482</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>481</v>
+      </c>
+      <c r="H29" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F28" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="G28" s="43">
-        <v>46237</v>
-      </c>
-      <c r="H28" s="43">
-        <v>46254</v>
-      </c>
-      <c r="I28" s="22" t="s">
-        <v>293</v>
-      </c>
-      <c r="J28" s="22" t="s">
+      <c r="I29" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="J29" s="41">
+        <v>46244</v>
+      </c>
+      <c r="K29" s="41">
+        <v>46258</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="M29" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K28" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="L28" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="M28" s="22" t="s">
-        <v>294</v>
-      </c>
-      <c r="N28" s="22" t="s">
-        <v>295</v>
-      </c>
-      <c r="O28" s="23" t="str">
+      <c r="N29" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="O29" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="P29" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q29" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="R29" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="36">
-      <c r="A29" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="B29" s="22" t="s">
+    <row r="30" spans="1:18" ht="36">
+      <c r="A30" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="B30" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C29" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" s="22" t="s">
-        <v>299</v>
-      </c>
-      <c r="G29" s="43">
+      <c r="C30" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>439</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I30" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="J30" s="41">
         <v>46244</v>
       </c>
-      <c r="H29" s="43">
-        <v>46258</v>
-      </c>
-      <c r="I29" s="22" t="s">
-        <v>300</v>
-      </c>
-      <c r="J29" s="22" t="s">
+      <c r="K30" s="41">
+        <v>46255</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="M30" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K29" s="22" t="s">
+      <c r="N30" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L29" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="M29" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="N29" s="22" t="s">
-        <v>302</v>
-      </c>
-      <c r="O29" s="23" t="str">
+      <c r="O30" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="P30" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q30" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="R30" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="36" hidden="1">
-      <c r="A30" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="B30" s="22" t="s">
+    <row r="31" spans="1:18" ht="36">
+      <c r="A31" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="B31" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C31" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="D30" s="22" t="s">
-        <v>304</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="G30" s="43">
-        <v>46244</v>
-      </c>
-      <c r="H30" s="43">
-        <v>46255</v>
-      </c>
-      <c r="I30" s="22" t="s">
-        <v>306</v>
-      </c>
-      <c r="J30" s="22" t="s">
+      <c r="D31" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>444</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="J31" s="41">
+        <v>46251</v>
+      </c>
+      <c r="K31" s="41">
+        <v>46262</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="M31" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K30" s="22" t="s">
+      <c r="N31" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L30" s="22" t="s">
+      <c r="O31" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M30" s="22" t="s">
-        <v>307</v>
-      </c>
-      <c r="N30" s="22" t="s">
-        <v>308</v>
-      </c>
-      <c r="O30" s="23" t="str">
+      <c r="P31" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q31" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="R31" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="36" hidden="1">
-      <c r="A31" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="B31" s="22" t="s">
+    <row r="32" spans="1:18" ht="36">
+      <c r="A32" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="B32" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C31" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>310</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="G31" s="43">
-        <v>46251</v>
-      </c>
-      <c r="H31" s="43">
-        <v>46262</v>
-      </c>
-      <c r="I31" s="22" t="s">
-        <v>312</v>
-      </c>
-      <c r="J31" s="22" t="s">
+      <c r="C32" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>447</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="J32" s="41">
+        <v>46252</v>
+      </c>
+      <c r="K32" s="41">
+        <v>46254</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="M32" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K31" s="22" t="s">
+      <c r="N32" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L31" s="22" t="s">
+      <c r="O32" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M31" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="N31" s="22" t="s">
-        <v>314</v>
-      </c>
-      <c r="O31" s="23" t="str">
+      <c r="P32" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q32" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="R32" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="36" hidden="1">
-      <c r="A32" s="21" t="s">
-        <v>315</v>
-      </c>
-      <c r="B32" s="22" t="s">
+    <row r="33" spans="1:18" ht="36">
+      <c r="A33" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="B33" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C32" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="22" t="s">
-        <v>317</v>
-      </c>
-      <c r="G32" s="43">
-        <v>46252</v>
-      </c>
-      <c r="H32" s="43">
-        <v>46254</v>
-      </c>
-      <c r="I32" s="22" t="s">
+      <c r="C33" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>444</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="J33" s="41">
+        <v>46259</v>
+      </c>
+      <c r="K33" s="41">
+        <v>46261</v>
+      </c>
+      <c r="L33" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="J32" s="22" t="s">
+      <c r="M33" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K32" s="22" t="s">
+      <c r="N33" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L32" s="22" t="s">
+      <c r="O33" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M32" s="22" t="s">
-        <v>318</v>
-      </c>
-      <c r="N32" s="22" t="s">
-        <v>319</v>
-      </c>
-      <c r="O32" s="23" t="str">
+      <c r="P33" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q33" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="R33" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="36" hidden="1">
-      <c r="A33" s="21" t="s">
-        <v>320</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>321</v>
-      </c>
-      <c r="E33" s="22" t="s">
+    <row r="34" spans="1:18" ht="36">
+      <c r="A34" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>499</v>
+      </c>
+      <c r="G34" s="20" t="s">
+        <v>498</v>
+      </c>
+      <c r="H34" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F33" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="G33" s="43">
-        <v>46259</v>
-      </c>
-      <c r="H33" s="43">
-        <v>46261</v>
-      </c>
-      <c r="I33" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="J33" s="22" t="s">
+      <c r="I34" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="J34" s="41">
+        <v>46265</v>
+      </c>
+      <c r="K34" s="41">
+        <v>46269</v>
+      </c>
+      <c r="L34" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="M34" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K33" s="22" t="s">
+      <c r="N34" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L33" s="22" t="s">
+      <c r="O34" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M33" s="22" t="s">
-        <v>322</v>
-      </c>
-      <c r="N33" s="22" t="s">
-        <v>323</v>
-      </c>
-      <c r="O33" s="23" t="str">
+      <c r="P34" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q34" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="R34" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="36" hidden="1">
-      <c r="A34" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="B34" s="22" t="s">
+    <row r="35" spans="1:18" ht="36">
+      <c r="A35" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="B35" s="20" t="s">
         <v>325</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C35" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="D34" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="22" t="s">
-        <v>328</v>
-      </c>
-      <c r="G34" s="43">
+      <c r="D35" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>502</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>501</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="I35" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="J35" s="41">
         <v>46265</v>
       </c>
-      <c r="H34" s="43">
-        <v>46269</v>
-      </c>
-      <c r="I34" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="J34" s="22" t="s">
+      <c r="K35" s="41">
+        <v>46273</v>
+      </c>
+      <c r="L35" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="M35" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K34" s="22" t="s">
+      <c r="N35" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L34" s="22" t="s">
+      <c r="O35" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M34" s="22" t="s">
-        <v>330</v>
-      </c>
-      <c r="N34" s="22" t="s">
-        <v>331</v>
-      </c>
-      <c r="O34" s="23" t="str">
+      <c r="P35" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q35" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="R35" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="36" hidden="1">
-      <c r="A35" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="B35" s="22" t="s">
+    <row r="36" spans="1:18" ht="36">
+      <c r="A36" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="B36" s="20" t="s">
         <v>325</v>
       </c>
-      <c r="C35" s="22" t="s">
-        <v>326</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>333</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="F35" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="G35" s="43">
-        <v>46265</v>
-      </c>
-      <c r="H35" s="43">
-        <v>46273</v>
-      </c>
-      <c r="I35" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="J35" s="22" t="s">
+      <c r="C36" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>486</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>485</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="J36" s="41">
+        <v>46266</v>
+      </c>
+      <c r="K36" s="41">
+        <v>46276</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="M36" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K35" s="22" t="s">
+      <c r="N36" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L35" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="M35" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="N35" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="O35" s="23" t="str">
+      <c r="O36" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="P36" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q36" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="R36" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="36">
-      <c r="A36" s="21" t="s">
-        <v>338</v>
-      </c>
-      <c r="B36" s="22" t="s">
+    <row r="37" spans="1:18" ht="36">
+      <c r="A37" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="B37" s="20" t="s">
         <v>325</v>
       </c>
-      <c r="C36" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>339</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="22" t="s">
-        <v>299</v>
-      </c>
-      <c r="G36" s="43">
-        <v>46266</v>
-      </c>
-      <c r="H36" s="43">
-        <v>46276</v>
-      </c>
-      <c r="I36" s="22" t="s">
-        <v>340</v>
-      </c>
-      <c r="J36" s="22" t="s">
+      <c r="C37" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>502</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>501</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="J37" s="41">
+        <v>46273</v>
+      </c>
+      <c r="K37" s="41">
+        <v>46275</v>
+      </c>
+      <c r="L37" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="M37" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K36" s="22" t="s">
+      <c r="N37" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L36" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="M36" s="22" t="s">
-        <v>341</v>
-      </c>
-      <c r="N36" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="O36" s="23" t="str">
+      <c r="O37" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="P37" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q37" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="R37" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="36" hidden="1">
-      <c r="A37" s="21" t="s">
-        <v>343</v>
-      </c>
-      <c r="B37" s="22" t="s">
+    <row r="38" spans="1:18" ht="36">
+      <c r="A38" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="B38" s="20" t="s">
         <v>325</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C38" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="D37" s="22" t="s">
-        <v>344</v>
-      </c>
-      <c r="E37" s="22" t="s">
+      <c r="D38" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>509</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>508</v>
+      </c>
+      <c r="H38" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F37" s="22" t="s">
-        <v>345</v>
-      </c>
-      <c r="G37" s="43">
-        <v>46273</v>
-      </c>
-      <c r="H37" s="43">
-        <v>46275</v>
-      </c>
-      <c r="I37" s="22" t="s">
-        <v>346</v>
-      </c>
-      <c r="J37" s="22" t="s">
+      <c r="I38" s="20" t="s">
+        <v>535</v>
+      </c>
+      <c r="J38" s="41">
+        <v>46272</v>
+      </c>
+      <c r="K38" s="41">
+        <v>46280</v>
+      </c>
+      <c r="L38" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="M38" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K37" s="22" t="s">
+      <c r="N38" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L37" s="22" t="s">
+      <c r="O38" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M37" s="22" t="s">
-        <v>347</v>
-      </c>
-      <c r="N37" s="22" t="s">
-        <v>348</v>
-      </c>
-      <c r="O37" s="23" t="str">
+      <c r="P38" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q38" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="R38" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="36" hidden="1">
-      <c r="A38" s="21" t="s">
-        <v>349</v>
-      </c>
-      <c r="B38" s="22" t="s">
+    <row r="39" spans="1:18" ht="36">
+      <c r="A39" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="B39" s="20" t="s">
         <v>325</v>
       </c>
-      <c r="C38" s="22" t="s">
+      <c r="C39" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="D38" s="22" t="s">
-        <v>350</v>
-      </c>
-      <c r="E38" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F38" s="22" t="s">
-        <v>537</v>
-      </c>
-      <c r="G38" s="43">
-        <v>46272</v>
-      </c>
-      <c r="H38" s="43">
-        <v>46280</v>
-      </c>
-      <c r="I38" s="22" t="s">
-        <v>351</v>
-      </c>
-      <c r="J38" s="22" t="s">
+      <c r="D39" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>513</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>512</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="J39" s="41">
+        <v>46275</v>
+      </c>
+      <c r="K39" s="41">
+        <v>46283</v>
+      </c>
+      <c r="L39" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="M39" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="K38" s="22" t="s">
+      <c r="N39" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="L38" s="22" t="s">
+      <c r="O39" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="M38" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="N38" s="22" t="s">
-        <v>353</v>
-      </c>
-      <c r="O38" s="23" t="str">
+      <c r="P39" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q39" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="R39" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="36" hidden="1">
-      <c r="A39" s="21" t="s">
-        <v>354</v>
-      </c>
-      <c r="B39" s="22" t="s">
+    <row r="40" spans="1:18" ht="36">
+      <c r="A40" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="B40" s="23" t="s">
         <v>325</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C40" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="D39" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="F39" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="G39" s="43">
-        <v>46275</v>
-      </c>
-      <c r="H39" s="43">
+      <c r="D40" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>509</v>
+      </c>
+      <c r="G40" s="48" t="s">
+        <v>508</v>
+      </c>
+      <c r="H40" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="I40" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="J40" s="24">
+        <v>46281</v>
+      </c>
+      <c r="K40" s="24">
         <v>46283</v>
       </c>
-      <c r="I39" s="22" t="s">
-        <v>357</v>
-      </c>
-      <c r="J39" s="22" t="s">
+      <c r="L40" s="23" t="s">
+        <v>363</v>
+      </c>
+      <c r="M40" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="K39" s="22" t="s">
+      <c r="N40" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="L39" s="22" t="s">
+      <c r="O40" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M39" s="22" t="s">
-        <v>358</v>
-      </c>
-      <c r="N39" s="22" t="s">
-        <v>359</v>
-      </c>
-      <c r="O39" s="23" t="str">
+      <c r="P40" s="23" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q40" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="R40" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>On Track</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="36" hidden="1">
-      <c r="A40" s="24" t="s">
-        <v>360</v>
-      </c>
-      <c r="B40" s="25" t="s">
-        <v>325</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>326</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>361</v>
-      </c>
-      <c r="E40" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="25" t="s">
-        <v>362</v>
-      </c>
-      <c r="G40" s="26">
-        <v>46281</v>
-      </c>
-      <c r="H40" s="26">
-        <v>46283</v>
-      </c>
-      <c r="I40" s="25" t="s">
-        <v>363</v>
-      </c>
-      <c r="J40" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="K40" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="L40" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="M40" s="25" t="s">
-        <v>364</v>
-      </c>
-      <c r="N40" s="25" t="s">
-        <v>365</v>
-      </c>
-      <c r="O40" s="27" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>On Track</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K40">
+  <phoneticPr fontId="15" type="noConversion"/>
+  <conditionalFormatting sqref="N2:N40">
     <cfRule type="expression" dxfId="5" priority="1">
-      <formula>K2="Red"</formula>
+      <formula>N2="Red"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="2">
-      <formula>K2="Amber"</formula>
+      <formula>N2="Amber"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="3">
-      <formula>K2="Green"</formula>
+      <formula>N2="Green"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O40">
+  <conditionalFormatting sqref="R2:R40">
     <cfRule type="expression" dxfId="2" priority="4">
-      <formula>$O2="Overdue"</formula>
+      <formula>$R2="Overdue"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="5">
-      <formula>$O2="Due &lt;=7d"</formula>
+      <formula>$R2="Due &lt;=7d"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="6">
-      <formula>$O2="On Track"</formula>
+      <formula>$R2="On Track"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" sqref="J2:J40" xr:uid="{00000000-0002-0000-0300-000000000000}">
+  <dataValidations count="11">
+    <dataValidation type="list" sqref="M2:M40" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Done,Deferred"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="K2:K40" xr:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation type="list" sqref="N2:N40" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"Green,Amber,Red"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2:L40" xr:uid="{00000000-0002-0000-0300-000002000000}">
+    <dataValidation type="list" sqref="O2:O40" xr:uid="{00000000-0002-0000-0300-000002000000}">
       <formula1>"Must Have,Should Have,Good to Have"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F9" xr:uid="{011A82D4-72B5-440C-8F37-3963010B58A4}">
+      <formula1>_xlfn.ANCHORARRAY($T$2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F12 F21:F23 F16" xr:uid="{E21CCABD-3A1B-493D-B609-72EDB8C72567}">
+      <formula1>_xlfn.ANCHORARRAY($U$2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F17:F19 F13:F15" xr:uid="{A7FB415F-9A00-47D5-BDA6-FB2D302A1D8F}">
+      <formula1>_xlfn.ANCHORARRAY($V$2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F33 F24:F25 F30:F31" xr:uid="{BE26509D-2E60-4D66-A02A-5E543FF88AA1}">
+      <formula1>_xlfn.ANCHORARRAY($W$2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F32 F26:F27" xr:uid="{5D1F0647-1666-4F60-BDC5-5250A13D03F6}">
+      <formula1>_xlfn.ANCHORARRAY($X$2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F28 F20" xr:uid="{CBA04805-FDC4-4739-957F-2EEAF6FC2A69}">
+      <formula1>_xlfn.ANCHORARRAY($Y$2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F37:F40 F34:F35" xr:uid="{1C9B6C07-7A4F-4FD5-B2B9-A04882E91507}">
+      <formula1>_xlfn.ANCHORARRAY($Z$2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F36 F29" xr:uid="{8A88C87B-C065-4049-B082-581D3DD222EA}">
+      <formula1>_xlfn.ANCHORARRAY($AA$2)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8127,10 +9100,10 @@
         <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="26.4">
@@ -8150,10 +9123,10 @@
         <v>131</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26.4">
@@ -8173,21 +9146,21 @@
         <v>184</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26.4">
       <c r="A4" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>526</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>267</v>
@@ -8196,10 +9169,10 @@
         <v>202</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26.4">
@@ -8215,15 +9188,15 @@
         <v>268</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="26.4">
       <c r="A6" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -8232,10 +9205,10 @@
         <v>236</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26.4">
@@ -8247,10 +9220,10 @@
         <v>243</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="26.4">
@@ -8262,7 +9235,7 @@
         <v>326</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -8275,7 +9248,7 @@
         <v>297</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G9" s="2"/>
     </row>
@@ -8288,21 +9261,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005181C5F62C4B5A4CB7444FB33AD1D1FE" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6d4dd119e202e01b28fe9e56f7a55439">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="936b0a21-3754-46bd-ad12-cf9d8277a26f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac4160e04c183f40edaf337bade30ad1" ns2:_="">
     <xsd:import namespace="936b0a21-3754-46bd-ad12-cf9d8277a26f"/>
@@ -8440,31 +9398,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3051BC0C-BFCC-44E8-AF02-AF50E40F3BAC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="936b0a21-3754-46bd-ad12-cf9d8277a26f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30441684-71FD-4BEA-8050-9D1965956EF0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94B182C7-6231-43FA-9587-4C0A65B1BDCE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8480,4 +9429,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3051BC0C-BFCC-44E8-AF02-AF50E40F3BAC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="936b0a21-3754-46bd-ad12-cf9d8277a26f"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30441684-71FD-4BEA-8050-9D1965956EF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>